--- a/Result/profitability/9958.xlsx
+++ b/Result/profitability/9958.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4375</v>
+        <v>1.40625</v>
       </c>
       <c r="N2" t="n">
-        <v>25.81625</v>
+        <v>24.14125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2475</v>
+        <v>1.375</v>
       </c>
       <c r="N3" t="n">
-        <v>23.44875</v>
+        <v>24.545</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>1.19625</v>
+        <v>1.20125</v>
       </c>
       <c r="N4" t="n">
-        <v>22.8575</v>
+        <v>22.26875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>0.9175</v>
       </c>
       <c r="N5" t="n">
-        <v>20.1475</v>
+        <v>18.3625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.73875</v>
+        <v>0.7737499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>16.28875</v>
+        <v>15.475</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5962499999999999</v>
+        <v>0.55625</v>
       </c>
       <c r="N7" t="n">
-        <v>13.3825</v>
+        <v>11.98125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0.41375</v>
+        <v>0.26625</v>
       </c>
       <c r="N8" t="n">
-        <v>10.3575</v>
+        <v>8.706250000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.0975</v>
       </c>
       <c r="N9" t="n">
-        <v>7.2575</v>
+        <v>7.257499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.065</v>
       </c>
       <c r="N13" t="n">
-        <v>5.393750000000001</v>
+        <v>5.39375</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9958</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5613</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4491</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1122</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>890</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>868</v>
+      </c>
+      <c r="K75" t="n">
+        <v>357</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.59375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.79875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4486692015209125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-13.21</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3980114492316963</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3378995433789954</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-14.28</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4168126094570928</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
